--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 бррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 бррсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\06,10,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694C6F32-D029-454B-BFEA-5613E3095670}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCA3A3E-C4C8-43BD-B910-3C523DE992AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,7 +453,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +485,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +530,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -547,6 +553,7 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3164,7 +3171,7 @@
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>1633</v>
+        <v>1609</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
@@ -3728,9 +3735,8 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="T10" s="8">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T10" s="22">
+        <v>0</v>
       </c>
       <c r="U10" s="20"/>
       <c r="V10" s="6" t="e">
@@ -3839,9 +3845,8 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="T11" s="8">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T11" s="22">
+        <v>0</v>
       </c>
       <c r="U11" s="20"/>
       <c r="V11" s="6" t="e">

--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 бррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 бррсч ост сыр.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\06,10,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCA3A3E-C4C8-43BD-B910-3C523DE992AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84CB87D-761A-485A-AC93-0E81609D100E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
